--- a/excel/piece_count_distribution.xlsx
+++ b/excel/piece_count_distribution.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monfalcone\PycharmProjects\TinyMLInternship\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monfalcone\PycharmProjects\TinyMLInternship\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0558FD5D-B7BB-4B70-BA50-BD2D030881BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEF3C04-03E1-4DEE-9CCA-6EE5EF084405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2098,6 +2098,14 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D32">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2108,14 +2116,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
